--- a/data/trans_orig/IP11A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11A_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3529</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3529</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3529</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3529</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,107 +1066,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2587</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2526</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15573</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13450</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13363</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15573</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13473</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>13363</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>13363</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>13363</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8794</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8794</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8794</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8794</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4210</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>34,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11030</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8241</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>9618</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11030</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>9618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>9618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>9618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,92 +2095,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4861</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44699</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41550</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44699</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41664</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46044</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>76926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8569</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10712</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8569</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6572</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10712</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>10712</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>10712</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,102 +3018,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2647</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4714</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27610</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24927</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17760</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15595</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>18470</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>84,44%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27610</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>25591</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41993</t>
+          <t>42033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>18470</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>18470</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>18470</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,107 +3356,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1251</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4637</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5294</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5696</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>11207</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11207</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7821</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10777</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3812,47 +3812,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>11754</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>11754</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>11754</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>11754</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70856</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72751</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>51002</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47478</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>48168</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>70856</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>65510</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>72745</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>176</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>124376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1119</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1119</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5073,47 +5073,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6346</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>6346</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>6346</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>6346</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1257</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3935</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5008</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>6265</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>79,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6265</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>6265</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>6265</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4745</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1493</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4138</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9670</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>8146</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5833</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>9639</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>60,51%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13114</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10277</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>71,29%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>9639</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>9639</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>9639</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36720</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20618</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17089</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22604</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22591</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,23%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39423</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36683</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56670</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>62665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3068</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -7025,34 +7025,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>45,74%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6690</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2865</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>35,51%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7207</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7797</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>64,49%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9436</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -8049,74 +8049,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20694</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15807</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15903</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22324</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
